--- a/data/analysis_pixtral_12b_panns/multimodal_event_eval_pixtral_12b_panns_w2_5s_h1_25s.xlsx
+++ b/data/analysis_pixtral_12b_panns/multimodal_event_eval_pixtral_12b_panns_w2_5s_h1_25s.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="54">
   <si>
     <t>event</t>
   </si>
@@ -112,46 +112,49 @@
     <t>NO</t>
   </si>
   <si>
-    <t>sound: speech(0-210), sound: animal(120-180), sound: engine(180-240), visual: carrying(216-216), visual: carrying(168-168), visual: carrying(192-192), visual: carrying(120-120)</t>
+    <t>sound: engine(180-240), visual: carrying(216-216), visual: carrying(168-168), visual: carrying(192-192), visual: carrying(120-120)</t>
+  </si>
+  <si>
+    <t>gunshot_or_explosion(90-240)</t>
+  </si>
+  <si>
+    <t>sound: gunshot_or_explosion(90-180), sound: engine(150-240), visual: carrying(168-192), visual: explosion_visible(144-240), visual: explosion_visible(168-168), visual: explosion_visible(192-240), visual: explosion_visible(120-120), visual: explosion_visible(144-240), visual: running(120-144), visual: running(144-240), visual: suspicious_near_vehicle(48-72), visual: suspicious_near_vehicle(0-24), visual: suspicious_near_vehicle(96-120), visual: suspicious_near_vehicle(192-192), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(120-120), visual: suspicious_near_vehicle(48-72), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(96-96), visual: vehicle_collision(120-240)</t>
+  </si>
+  <si>
+    <t>gunshot_or_explosion(30-120)</t>
   </si>
   <si>
     <t>gunshot_or_explosion(120-240)</t>
   </si>
   <si>
-    <t>sound: speech(0-120), sound: burst_pop(90-150), sound: gunshot_or_explosion(120-180), sound: engine(150-240), visual: carrying(168-192), visual: explosion_visible(144-240), visual: explosion_visible(168-168), visual: explosion_visible(192-240), visual: explosion_visible(120-120), visual: explosion_visible(144-240), visual: running(120-144), visual: running(144-240), visual: suspicious_near_vehicle(48-72), visual: suspicious_near_vehicle(0-24), visual: suspicious_near_vehicle(96-120), visual: suspicious_near_vehicle(192-192), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(120-120), visual: suspicious_near_vehicle(48-72), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(96-96), visual: vehicle_collision(120-240)</t>
-  </si>
-  <si>
-    <t>gunshot_or_explosion(60-120)</t>
-  </si>
-  <si>
     <t>gunshot_or_explosion(0-240)</t>
   </si>
   <si>
-    <t>sound: gunshot_or_explosion(0-90), sound: speech(60-150), sound: engine(120-240), visual: enter_or_exit_vehicle(0-24), visual: explosion_visible(48-240), visual: explosion_visible(144-240), visual: explosion_visible(48-72), visual: explosion_visible(144-240), visual: explosion_visible(216-240), visual: running(144-240), visual: suspicious_near_vehicle(0-24), visual: vehicle_collision(0-240)</t>
-  </si>
-  <si>
-    <t>sound: door(0-90), sound: engine(60-240), visual: enter_or_exit_vehicle(48-48), visual: suspicious_near_vehicle(48-48), visual: suspicious_near_vehicle(168-168)</t>
-  </si>
-  <si>
-    <t>sound: tick_tock(0-60), sound: shuffle(30-90), sound: engine(60-240)</t>
-  </si>
-  <si>
-    <t>sound: animal(0-60), sound: door(30-90), sound: engine(60-240), visual: enter_or_exit_vehicle(48-48), visual: suspicious_near_vehicle(0-48), visual: suspicious_near_vehicle(168-168), visual: vehicle_collision(168-168)</t>
-  </si>
-  <si>
-    <t>sound: horn(0-90), sound: breaking(60-150), sound: engine(120-210), sound: door(180-240), visual: carrying(48-48), visual: enter_or_exit_vehicle(192-192), visual: suspicious_near_vehicle(72-96), visual: suspicious_near_vehicle(192-192), visual: suspicious_near_vehicle(96-96), visual: suspicious_near_vehicle(72-96), visual: suspicious_near_vehicle(72-96), visual: suspicious_near_vehicle(96-96)</t>
+    <t>sound: gunshot_or_explosion(0-90), sound: engine(120-240), visual: enter_or_exit_vehicle(0-24), visual: explosion_visible(48-240), visual: explosion_visible(144-240), visual: explosion_visible(48-72), visual: explosion_visible(144-240), visual: explosion_visible(216-240), visual: running(144-240), visual: suspicious_near_vehicle(0-24), visual: vehicle_collision(0-240)</t>
+  </si>
+  <si>
+    <t>sound: engine(60-240), visual: enter_or_exit_vehicle(48-48), visual: suspicious_near_vehicle(48-48), visual: suspicious_near_vehicle(168-168)</t>
+  </si>
+  <si>
+    <t>sound: engine(60-240)</t>
+  </si>
+  <si>
+    <t>sound: engine(60-240), visual: enter_or_exit_vehicle(48-48), visual: suspicious_near_vehicle(0-48), visual: suspicious_near_vehicle(168-168), visual: vehicle_collision(168-168)</t>
+  </si>
+  <si>
+    <t>sound: horn(0-90), sound: engine(120-210), visual: carrying(48-48), visual: enter_or_exit_vehicle(192-192), visual: suspicious_near_vehicle(72-96), visual: suspicious_near_vehicle(192-192), visual: suspicious_near_vehicle(96-96), visual: suspicious_near_vehicle(72-96), visual: suspicious_near_vehicle(72-96), visual: suspicious_near_vehicle(96-96)</t>
   </si>
   <si>
     <t>vehicle_collision(30-240)</t>
   </si>
   <si>
-    <t>sound: engine(0-60), sound: skidding(30-90), sound: gunshot_or_explosion(60-120), sound: glass_breaking(90-150), sound: speech(120-240), visual: enter_or_exit_vehicle(144-144), visual: enter_or_exit_vehicle(240-240), visual: running(24-240), visual: suspicious_near_vehicle(120-240), visual: suspicious_near_vehicle(96-96), visual: suspicious_near_vehicle(120-120), visual: vehicle_collision(72-240), visual: vehicle_collision(72-72), visual: vehicle_collision(96-216)</t>
+    <t>sound: engine(0-60), sound: skidding(30-90), sound: gunshot_or_explosion(60-120), sound: glass_breaking(90-150), visual: enter_or_exit_vehicle(144-144), visual: enter_or_exit_vehicle(240-240), visual: running(24-240), visual: suspicious_near_vehicle(120-240), visual: suspicious_near_vehicle(96-96), visual: suspicious_near_vehicle(120-120), visual: vehicle_collision(72-240), visual: vehicle_collision(72-72), visual: vehicle_collision(96-216)</t>
   </si>
   <si>
     <t>vehicle_collision(120-240)</t>
   </si>
   <si>
-    <t>sound: horn(0-60), sound: engine(30-240), sound: gunshot_or_explosion(60-120), sound: breaking(90-150), visual: enter_or_exit_vehicle(120-216), visual: enter_or_exit_vehicle(144-144), visual: enter_or_exit_vehicle(120-216), visual: suspicious_near_vehicle(168-240), visual: suspicious_near_vehicle(144-144), visual: suspicious_near_vehicle(168-240), visual: vehicle_collision(120-240), visual: vehicle_collision(192-240)</t>
+    <t>sound: horn(0-60), sound: engine(30-240), sound: gunshot_or_explosion(60-120), visual: enter_or_exit_vehicle(120-216), visual: enter_or_exit_vehicle(144-144), visual: enter_or_exit_vehicle(120-216), visual: suspicious_near_vehicle(168-240), visual: suspicious_near_vehicle(144-144), visual: suspicious_near_vehicle(168-240), visual: vehicle_collision(120-240), visual: vehicle_collision(192-240)</t>
   </si>
   <si>
     <t>visual: enter_or_exit_vehicle(24-48), visual: enter_or_exit_vehicle(192-216), visual: suspicious_near_vehicle(24-144), visual: suspicious_near_vehicle(168-216)</t>
@@ -175,7 +178,7 @@
     <t>handoff(0-24), handoff(24-192), handoff(0-24), handoff(24-192)</t>
   </si>
   <si>
-    <t>sound: speech(0-180), sound: silence(150-210), sound: sigh(180-240), visual: physical_altercation(48-120), visual: physical_altercation(144-168)</t>
+    <t>visual: physical_altercation(48-120), visual: physical_altercation(144-168)</t>
   </si>
   <si>
     <t>fight(48-120)</t>
@@ -187,7 +190,7 @@
     <t>vehicle_escape(0-168)</t>
   </si>
   <si>
-    <t>sound: animal(0-60), sound: door(30-90), sound: engine(60-240), visual: enter_or_exit_vehicle(48-168), visual: running(0-0), visual: suspicious_near_vehicle(0-168)</t>
+    <t>sound: engine(60-240), visual: enter_or_exit_vehicle(48-168), visual: running(0-0), visual: suspicious_near_vehicle(0-168)</t>
   </si>
   <si>
     <t>vehicle_collision(72-240)</t>
@@ -786,7 +789,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -830,7 +833,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -874,7 +877,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -891,7 +894,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -935,7 +938,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -979,7 +982,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -996,7 +999,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1040,7 +1043,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1057,7 +1060,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1101,7 +1104,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1145,7 +1148,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1189,7 +1192,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1206,7 +1209,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1250,7 +1253,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1338,7 +1341,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1382,7 +1385,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1426,7 +1429,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1470,7 +1473,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1514,7 +1517,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1558,7 +1561,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1575,7 +1578,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1619,7 +1622,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1663,7 +1666,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1707,7 +1710,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1751,7 +1754,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
@@ -1839,7 +1842,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -1883,7 +1886,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -2076,7 +2079,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -2120,7 +2123,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -2164,7 +2167,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -2181,7 +2184,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/data/analysis_pixtral_12b_panns/multimodal_event_eval_pixtral_12b_panns_w2_5s_h1_25s.xlsx
+++ b/data/analysis_pixtral_12b_panns/multimodal_event_eval_pixtral_12b_panns_w2_5s_h1_25s.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="51">
   <si>
     <t>event</t>
   </si>
@@ -103,10 +103,10 @@
     <t>YES</t>
   </si>
   <si>
-    <t>fight(24-144)</t>
-  </si>
-  <si>
-    <t>fight(48-168)</t>
+    <t>sound: engine(150-210), visual: physical_altercation(24-144), visual: physical_altercation(144-144), visual: running(144-144), visual: running(72-144), visual: running(144-144)</t>
+  </si>
+  <si>
+    <t>visual: physical_altercation(48-96), visual: physical_altercation(144-168), visual: physical_altercation(120-120), visual: physical_altercation(144-168), visual: running(72-72), visual: suspicious_near_vehicle(0-48), visual: suspicious_near_vehicle(0-48), visual: suspicious_near_vehicle(72-120), visual: suspicious_near_vehicle(120-120)</t>
   </si>
   <si>
     <t>NO</t>
@@ -115,19 +115,16 @@
     <t>sound: engine(180-240), visual: carrying(216-216), visual: carrying(168-168), visual: carrying(192-192), visual: carrying(120-120)</t>
   </si>
   <si>
-    <t>gunshot_or_explosion(90-240)</t>
-  </si>
-  <si>
     <t>sound: gunshot_or_explosion(90-180), sound: engine(150-240), visual: carrying(168-192), visual: explosion_visible(144-240), visual: explosion_visible(168-168), visual: explosion_visible(192-240), visual: explosion_visible(120-120), visual: explosion_visible(144-240), visual: running(120-144), visual: running(144-240), visual: suspicious_near_vehicle(48-72), visual: suspicious_near_vehicle(0-24), visual: suspicious_near_vehicle(96-120), visual: suspicious_near_vehicle(192-192), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(120-120), visual: suspicious_near_vehicle(48-72), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(96-96), visual: vehicle_collision(120-240)</t>
   </si>
   <si>
-    <t>gunshot_or_explosion(30-120)</t>
-  </si>
-  <si>
-    <t>gunshot_or_explosion(120-240)</t>
-  </si>
-  <si>
-    <t>gunshot_or_explosion(0-240)</t>
+    <t>sound: engine(0-60), sound: gunshot_or_explosion(30-120), visual: enter_or_exit_vehicle(72-72), visual: enter_or_exit_vehicle(120-120), visual: enter_or_exit_vehicle(0-0), visual: suspicious_near_vehicle(72-120), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(72-72)</t>
+  </si>
+  <si>
+    <t>sound: engine(0-60), sound: engine(150-240), sound: gunshot_or_explosion(120-180), visual: enter_or_exit_vehicle(48-48), visual: enter_or_exit_vehicle(96-96), visual: explosion_visible(120-240), visual: gunshot_visible(120-240), visual: running(120-240), visual: suspicious_near_vehicle(48-72), visual: suspicious_near_vehicle(144-144), visual: suspicious_near_vehicle(168-216), visual: suspicious_near_vehicle(96-120), visual: suspicious_near_vehicle(240-240), visual: suspicious_near_vehicle(144-216)</t>
+  </si>
+  <si>
+    <t>sound: gunshot_or_explosion(0-90), sound: engine(60-120), sound: engine(180-240), visual: explosion_visible(120-120), visual: explosion_visible(120-120), visual: explosion_visible(48-48), visual: explosion_visible(168-168), visual: explosion_visible(24-240), visual: explosion_visible(120-240), visual: explosion_visible(192-240), visual: running(48-240), visual: running(120-240), visual: running(120-240)</t>
   </si>
   <si>
     <t>sound: gunshot_or_explosion(0-90), sound: engine(120-240), visual: enter_or_exit_vehicle(0-24), visual: explosion_visible(48-240), visual: explosion_visible(144-240), visual: explosion_visible(48-72), visual: explosion_visible(144-240), visual: explosion_visible(216-240), visual: running(144-240), visual: suspicious_near_vehicle(0-24), visual: vehicle_collision(0-240)</t>
@@ -145,25 +142,16 @@
     <t>sound: horn(0-90), sound: engine(120-210), visual: carrying(48-48), visual: enter_or_exit_vehicle(192-192), visual: suspicious_near_vehicle(72-96), visual: suspicious_near_vehicle(192-192), visual: suspicious_near_vehicle(96-96), visual: suspicious_near_vehicle(72-96), visual: suspicious_near_vehicle(72-96), visual: suspicious_near_vehicle(96-96)</t>
   </si>
   <si>
-    <t>vehicle_collision(30-240)</t>
-  </si>
-  <si>
     <t>sound: engine(0-60), sound: skidding(30-90), sound: gunshot_or_explosion(60-120), sound: glass_breaking(90-150), visual: enter_or_exit_vehicle(144-144), visual: enter_or_exit_vehicle(240-240), visual: running(24-240), visual: suspicious_near_vehicle(120-240), visual: suspicious_near_vehicle(96-96), visual: suspicious_near_vehicle(120-120), visual: vehicle_collision(72-240), visual: vehicle_collision(72-72), visual: vehicle_collision(96-216)</t>
   </si>
   <si>
-    <t>vehicle_collision(120-240)</t>
-  </si>
-  <si>
     <t>sound: horn(0-60), sound: engine(30-240), sound: gunshot_or_explosion(60-120), visual: enter_or_exit_vehicle(120-216), visual: enter_or_exit_vehicle(144-144), visual: enter_or_exit_vehicle(120-216), visual: suspicious_near_vehicle(168-240), visual: suspicious_near_vehicle(144-144), visual: suspicious_near_vehicle(168-240), visual: vehicle_collision(120-240), visual: vehicle_collision(192-240)</t>
   </si>
   <si>
     <t>visual: enter_or_exit_vehicle(24-48), visual: enter_or_exit_vehicle(192-216), visual: suspicious_near_vehicle(24-144), visual: suspicious_near_vehicle(168-216)</t>
   </si>
   <si>
-    <t>loitering(24-216)</t>
-  </si>
-  <si>
-    <t>loitering(0-240)</t>
+    <t>visual: carrying(24-48), visual: suspicious_near_vehicle(24-216)</t>
   </si>
   <si>
     <t>visual: carrying(144-192), visual: enter_or_exit_vehicle(96-192), visual: running(72-120), visual: suspicious_near_vehicle(0-240)</t>
@@ -172,37 +160,40 @@
     <t>visual: carrying(24-48), visual: carrying(0-0), visual: carrying(144-240), visual: carrying(72-120), visual: carrying(168-240), visual: carrying(72-144)</t>
   </si>
   <si>
-    <t>handoff(120-216), handoff(0-120), handoff(0-120), handoff(0-168), handoff(120-216), handoff(0-120), handoff(0-120), handoff(0-168)</t>
-  </si>
-  <si>
-    <t>handoff(0-24), handoff(24-192), handoff(0-24), handoff(24-192)</t>
+    <t>visual: carrying(96-96), visual: carrying(240-240), visual: carrying(144-216), visual: carrying(0-120), visual: carrying(120-120), visual: carrying(144-144), visual: carrying(24-24), visual: carrying(96-96), visual: carrying(168-168), visual: carrying(192-240), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(216-216), visual: suspicious_near_vehicle(240-240), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(216-216), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(216-216), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(216-216), visual: suspicious_near_vehicle(216-216)</t>
+  </si>
+  <si>
+    <t>visual: carrying(0-0), visual: carrying(120-192), visual: carrying(48-96), visual: carrying(72-72), visual: carrying(24-24), visual: carrying(144-192), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(96-96), visual: suspicious_near_vehicle(192-192), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(0-0), visual: suspicious_near_vehicle(96-96), visual: suspicious_near_vehicle(192-192), visual: suspicious_near_vehicle(24-24), visual: suspicious_near_vehicle(48-72), visual: suspicious_near_vehicle(48-48)</t>
   </si>
   <si>
     <t>visual: physical_altercation(48-120), visual: physical_altercation(144-168)</t>
   </si>
   <si>
-    <t>fight(48-120)</t>
-  </si>
-  <si>
-    <t>vehicle_escape(24-72)</t>
-  </si>
-  <si>
-    <t>vehicle_escape(0-168)</t>
+    <t>visual: physical_altercation(48-120), visual: running(24-120), visual: running(192-192), visual: running(24-120), visual: running(192-192)</t>
+  </si>
+  <si>
+    <t>sound: engine(90-240), visual: carrying(48-72), visual: carrying(0-24), visual: carrying(120-144), visual: enter_or_exit_vehicle(72-72), visual: running(24-24), visual: suspicious_near_vehicle(0-48)</t>
   </si>
   <si>
     <t>sound: engine(60-240), visual: enter_or_exit_vehicle(48-168), visual: running(0-0), visual: suspicious_near_vehicle(0-168)</t>
   </si>
   <si>
-    <t>vehicle_collision(72-240)</t>
-  </si>
-  <si>
-    <t>loitering(0-216)</t>
-  </si>
-  <si>
-    <t>loitering(24-240)</t>
-  </si>
-  <si>
-    <t>handoff(0-48), handoff(0-168), handoff(24-240), handoff(120-240), handoff(0-48), handoff(24-240), handoff(0-168), handoff(120-240)</t>
+    <t>visual: enter_or_exit_vehicle(48-168), visual: running(0-0), visual: suspicious_near_vehicle(0-168)</t>
+  </si>
+  <si>
+    <t>sound: horn(0-90), sound: engine(120-210), visual: 9(216-216), visual: 9(216-216), visual: enter_or_exit_vehicle(168-216), visual: suspicious_near_vehicle(168-240), visual: vehicle_collision(72-240), visual: vehicle_collision(144-144), visual: vehicle_collision(96-120), visual: vehicle_collision(192-240), visual: vehicle_collision(72-72), visual: vehicle_collision(168-168)</t>
+  </si>
+  <si>
+    <t>sound: skidding(0-90), visual: enter_or_exit_vehicle(168-168), visual: suspicious_near_vehicle(168-240), visual: vehicle_collision(72-120), visual: vehicle_collision(72-240)</t>
+  </si>
+  <si>
+    <t>visual: carrying(0-24), visual: carrying(48-192), visual: enter_or_exit_vehicle(72-144), visual: running(216-216), visual: suspicious_near_vehicle(0-216)</t>
+  </si>
+  <si>
+    <t>visual: enter_or_exit_vehicle(48-144), visual: running(192-216), visual: suspicious_near_vehicle(24-240)</t>
+  </si>
+  <si>
+    <t>visual: carrying(0-0), visual: carrying(144-240), visual: carrying(72-96), visual: carrying(24-48), visual: carrying(120-168)</t>
   </si>
   <si>
     <t>visual: carrying(192-240), visual: carrying(24-168), visual: carrying(144-144), visual: walking(192-192)</t>
@@ -789,6 +780,50 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
         <v>29</v>
       </c>
     </row>
@@ -797,35 +832,35 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
       <c r="C2" t="s">
         <v>21</v>
       </c>
@@ -834,50 +869,6 @@
       </c>
       <c r="E2" t="s">
         <v>30</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -894,6 +885,50 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
         <v>31</v>
       </c>
     </row>
@@ -902,87 +937,43 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>15</v>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>16</v>
       </c>
       <c r="B2" t="s">
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
       </c>
       <c r="E2" t="s">
         <v>32</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>16</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -999,7 +990,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1043,7 +1034,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1060,139 +1051,139 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>19</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>20</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
         <v>36</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>18</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>19</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>20</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1209,6 +1200,226 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>21</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>22</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>29</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1217,40 +1428,40 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>21</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
       </c>
       <c r="E2" t="s">
         <v>41</v>
@@ -1261,78 +1472,34 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>22</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>31</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -1349,34 +1516,34 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>23</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>32</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -1386,182 +1553,6 @@
       </c>
       <c r="E2" t="s">
         <v>43</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>29</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>30</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>31</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>32</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1578,6 +1569,182 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>33</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>34</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>35</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1586,34 +1753,78 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>33</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>37</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
@@ -1630,263 +1841,43 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>34</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>35</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>38</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
       </c>
       <c r="E2" t="s">
         <v>50</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>36</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>51</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>37</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>38</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1991,6 +1982,50 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -1999,35 +2034,35 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
         <v>9</v>
       </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
       <c r="C2" t="s">
         <v>18</v>
       </c>
@@ -2043,35 +2078,35 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
         <v>9</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
       <c r="C2" t="s">
         <v>18</v>
       </c>
@@ -2080,50 +2115,6 @@
       </c>
       <c r="E2" t="s">
         <v>26</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" t="s">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -2184,7 +2175,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/data/analysis_pixtral_12b_panns/multimodal_event_eval_pixtral_12b_panns_w2_5s_h1_25s.xlsx
+++ b/data/analysis_pixtral_12b_panns/multimodal_event_eval_pixtral_12b_panns_w2_5s_h1_25s.xlsx
@@ -718,22 +718,22 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>0.667</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7">
         <v>1</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H7">
         <v>5</v>
@@ -1502,10 +1502,10 @@
         <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
       </c>
       <c r="E2" t="s">
         <v>42</v>
@@ -1546,10 +1546,10 @@
         <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
       </c>
       <c r="E2" t="s">
         <v>43</v>

--- a/data/analysis_pixtral_12b_panns/multimodal_event_eval_pixtral_12b_panns_w2_5s_h1_25s.xlsx
+++ b/data/analysis_pixtral_12b_panns/multimodal_event_eval_pixtral_12b_panns_w2_5s_h1_25s.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="52">
   <si>
     <t>event</t>
   </si>
@@ -143,6 +143,9 @@
   </si>
   <si>
     <t>sound: engine(0-60), sound: skidding(30-90), sound: gunshot_or_explosion(60-120), sound: glass_breaking(90-150), visual: enter_or_exit_vehicle(144-144), visual: enter_or_exit_vehicle(240-240), visual: running(24-240), visual: suspicious_near_vehicle(120-240), visual: suspicious_near_vehicle(96-96), visual: suspicious_near_vehicle(120-120), visual: vehicle_collision(72-240), visual: vehicle_collision(72-72), visual: vehicle_collision(96-216)</t>
+  </si>
+  <si>
+    <t>visual: enter_or_exit_vehicle(144-144), visual: enter_or_exit_vehicle(240-240), visual: running(24-240), visual: suspicious_near_vehicle(120-240), visual: suspicious_near_vehicle(96-96), visual: suspicious_near_vehicle(120-120), visual: vehicle_collision(72-240), visual: vehicle_collision(72-72), visual: vehicle_collision(96-216)</t>
   </si>
   <si>
     <t>sound: horn(0-60), sound: engine(30-240), sound: gunshot_or_explosion(60-120), visual: enter_or_exit_vehicle(120-216), visual: enter_or_exit_vehicle(144-144), visual: enter_or_exit_vehicle(120-216), visual: suspicious_near_vehicle(168-240), visual: suspicious_near_vehicle(144-144), visual: suspicious_near_vehicle(168-240), visual: vehicle_collision(120-240), visual: vehicle_collision(192-240)</t>
@@ -666,22 +669,22 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>0.8</v>
+        <v>0.714</v>
       </c>
       <c r="C5">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D5">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>5</v>
@@ -939,7 +942,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -993,6 +996,23 @@
         <v>32</v>
       </c>
     </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1034,7 +1054,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1051,7 +1071,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1089,13 +1109,13 @@
         <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" t="s">
-        <v>34</v>
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1139,7 +1159,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1183,7 +1203,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1200,7 +1220,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1244,7 +1264,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1332,7 +1352,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -1376,7 +1396,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1420,7 +1440,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1464,7 +1484,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1508,7 +1528,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -1552,7 +1572,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -1569,7 +1589,7 @@
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1613,7 +1633,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1657,7 +1677,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1701,7 +1721,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1745,7 +1765,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1833,7 +1853,7 @@
         <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1877,7 +1897,7 @@
         <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
